--- a/chat_history_log.xlsx
+++ b/chat_history_log.xlsx
@@ -1,75 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/abhay_singh2_bain_com/Documents/Documents/Python Scripts/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B59D2BFD3B05674E67EB313563088B35299F038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D54C2E0-BAF6-4087-A676-E630CFACFF11}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Answer</t>
-  </si>
-  <si>
-    <t>Sources</t>
-  </si>
-  <si>
-    <t>2025-05-29 08:01:31</t>
-  </si>
-  <si>
-    <t>Bain CEO?</t>
-  </si>
-  <si>
-    <t>As of February 2022, the CEO of Bain &amp; Company is Manny Maceda. Please note that this may change over time, so it's advisable to verify from the official Bain &amp; Company website for the most current information. 
-Source:
-"Bain &amp; Company Leadership". Bain &amp; Company. Retrieved from: https://www.bain.com/about/leadership/</t>
-  </si>
-  <si>
-    <t>Bain Overview FAQ.pdf (page 5), Full RFP FAQ Export.pdf (page 3), Bain Overview FAQ.pdf (page 2), Bain Overview FAQ.pdf (page 1), Full RFP FAQ Export.pdf (page 7), GRI report 2023.pdf (page 7), GRI report 2023.pdf (page 32), Bain Overview FAQ.pdf (page 6), Bain Overview FAQ.pdf (page 4), Full RFP FAQ Export.pdf (page 8), GRI report 2023.pdf (page 25), bain-wef-and-tcfd-report-2023.pdf (page 2), Bain Overview FAQ.pdf (page 3), Full RFP FAQ Export.pdf (page 5), Bain Overview FAQ.pdf (page 7), bain-wef-and-tcfd-report-2023.pdf (page 10), Full RFP FAQ Export.pdf (page 9), bain-wef-and-tcfd-report-2023.pdf (page 8), sustainable-procurement-factsheet-v3-05.02.2024.pdf (page 1), Full RFP FAQ Export.pdf (page 6)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -84,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -408,41 +420,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="255.77734375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-05-29 08:01:31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bain CEO?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>As of February 2022, the CEO of Bain &amp; Company is Manny Maceda. Please note that this may change over time, so it's advisable to verify from the official Bain &amp; Company website for the most current information. 
+Source:
+"Bain &amp; Company Leadership". Bain &amp; Company. Retrieved from: https://www.bain.com/about/leadership/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bain Overview FAQ.pdf (page 5), Full RFP FAQ Export.pdf (page 3), Bain Overview FAQ.pdf (page 2), Bain Overview FAQ.pdf (page 1), Full RFP FAQ Export.pdf (page 7), GRI report 2023.pdf (page 7), GRI report 2023.pdf (page 32), Bain Overview FAQ.pdf (page 6), Bain Overview FAQ.pdf (page 4), Full RFP FAQ Export.pdf (page 8), GRI report 2023.pdf (page 25), bain-wef-and-tcfd-report-2023.pdf (page 2), Bain Overview FAQ.pdf (page 3), Full RFP FAQ Export.pdf (page 5), Bain Overview FAQ.pdf (page 7), bain-wef-and-tcfd-report-2023.pdf (page 10), Full RFP FAQ Export.pdf (page 9), bain-wef-and-tcfd-report-2023.pdf (page 8), sustainable-procurement-factsheet-v3-05.02.2024.pdf (page 1), Full RFP FAQ Export.pdf (page 6)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/chat_history_log.xlsx
+++ b/chat_history_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,6 +694,257 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-05-30T09:39:10.826713</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bain emission by scope tabel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bain reports its Scope 1, Scope 2, and Scope 3 carbon emissions, including various categories under Scope 3, on an annual basis. Below is the reported data for the year 2023:
+Scope 1: Direct greenhouse gas emissions from assets owned or operated by the company, such as those from Company Owned Cars, Refrigerant gas losses, Natural gas, and Other fuel(s) - 1,510 tCO2e (tonnes of CO2 equivalent).
+Scope 2: Indirect greenhouse gas emissions resulting from the consumption of purchased electricity and fuel, such as Electricity, District heating and District cooling - 410 tCO2e.
+Scope 3: Categories included:
+• Category 1: Purchased goods and services 
+• Category 3: Fuel and energy-related activities not included in scope 1 or scope 2 
+• Category 5: Waste generated in operations 
+• Category 6: Business travel emissions, including emissions from air travel, hotels, buses, cars, taxis, and trains 
+• Category 7: Employee commuting - 171,643 tCO2e.
+Total Emissions: 173,563 tCO2e.
+(Source: 2023_carbon-credit-disclosure.pdf, page 6)
+Please note that the figures given are market-based emissions and do not include location-based emissions.
+Each of these emission categories are reported based on guidelines and methodologies from reputable environmental and sustainability institutions such as the World Business Council for Sustainable Development (WBCSD) and World Resources Institute’s (WRI) Greenhouse Gas Protocol, as well as conversion factors from the US EPA, IPCC, CIBSE, and other governments/international agencies (Source: GRI report 2023.pdf, page 61).
+These figures are obtained through Bain's tools and processes, and undergo external assurance to maintain their accuracy and transparency (Source: climate-transition-plan-2024.pdf, page 28).</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2023_carbon-credit-disclosure.pdf (page 6), GRI report 2023.pdf (page 61), climate-transition-plan-2024.pdf (page 15), GRI report 2023.pdf (page 61), climate-transition-plan-2024.pdf (page 16), bain-wef-and-tcfd-report-2023.pdf (page 29), climate-transition-plan-2024.pdf (page 11), GRI report 2023.pdf (page 21), climate-transition-plan-2024.pdf (page 27), GRI report 2023.pdf (page 22), climate-transition-plan-2024.pdf (page 9), climate-transition-plan-2024.pdf (page 13), GRI report 2023.pdf (page 60), climate-transition-plan-2024.pdf (page 12), climate-transition-plan-2024.pdf (page 28), Client RFP deck.pdf (page 36), bain-wef-and-tcfd-report-2023.pdf (page 6), Client RFP deck.pdf (page 38), bain-wef-and-tcfd-report-2023.pdf (page 6), Client RFP deck.pdf (page 35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-05-30T09:39:41.893587</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SBTI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The Science Based Targets initiative (SBTi) is a project that encourages companies to set science-based targets to reduce greenhouse gas emissions and limit global warming to below 2 degrees Celsius, in line with the Paris Agreement. 
+Bain &amp; Company has made various commitments aligned with the SBTi. Some of these commitments include:
+- Aiming to reach net-zero greenhouse gas emissions across the value chain by 2050. 
+- Reducing scope 1 and 2 emissions by 30% by 2026 from a 2019 base year and reducing scope 3 emissions from business travel by 35% per employee over the same time period. 
+- For the long-term, reducing absolute scope 1 and 2 GHG emissions by 90% by 2050 from a 2019 base year and further reducing scope 3 GHG emissions by 97% per FTE by 2050 from the same base year. 
+- Continuously sourcing 100% renewable electricity through 2050.
+- Working with suppliers to set their own SBTi targets, with a target of 65% of suppliers following suit by 2030.
+- A commitment to having a net-negative carbon impact, offsetting more than its annual carbon footprint.
+Furthermore, Bain is affiliated with SBTi and has been working with it to develop training materials to help companies set science-based targets (Environmental-policy.pdf, page 2; Client RFP deck.pdf, pages 32, 42, 47).</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Environmental-policy.pdf (page 2), Environmental-policy.pdf (page 4), Client RFP deck.pdf (page 47), GRI report 2023.pdf (page 17), GRI report 2023.pdf (page 61), GRI report 2023.pdf (page 32), GRI report 2023.pdf (page 3), Client RFP deck.pdf (page 32), Client RFP deck.pdf (page 42), Client RFP deck.pdf (page 47), Client RFP deck.pdf (page 37), Client RFP deck.pdf (page 50), Client RFP deck.pdf (page 64), Client RFP deck.pdf (page 76), Client RFP deck.pdf (page 27), Client RFP deck.pdf (page 26), Client RFP deck.pdf (page 29), Client RFP deck.pdf (page 67), Client RFP deck.pdf (page 48), Client RFP deck.pdf (page 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-05-30T09:40:10.696406</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>new hire</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>In 2023, Bain hired 3,427 new employees globally. In terms of gender, 52% of these new hires were male, 44% were female and 4% did not declare their gender. In terms of region, the specific numbers are not detailed, but the document lays out that Bain operates in the Americas, EMEA, and APAC regions [GRI report 2023.pdf, pages 64, 65, 66]. 
+Bain is committed to the professional development of its new hires. It provides a range of training and mentorship programs which are necessary to tackle emerging industry challenges. New joiners receive Health Safety and Security Employee (HSE) training during onboarding. New employees also have access to various learning resources and tools through a virtual learning platform, Springboard. To manage its talent strategy and ensure fairness, Bain implements initiatives such as fair hiring processes and inclusive practices [GRI report 2023.pdf, page 25].
+Moreover, Bain offers competitive benefits including options to enroll in healthcare plans at low or no cost, free access to well-being tools like Headspace and one-on-one counseling services. It also provides flexible working opportunities, such as virtual working arrangements, part-time work, and extended leaves of absence [GRI report 2023.pdf, page 25].
+Bain also follows a clear Equal Employment Opportunity policy that prohibits any form of discrimination with respect to employee hiring [GRI report 2023.pdf, page 24].</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GRI report 2023.pdf (page 27), GRI report 2023.pdf (page 25), GRI report 2023.pdf (page 24), GRI report 2023.pdf (page 66), GRI report 2023.pdf (page 65), GRI report 2023.pdf (page 29), GRI report 2023.pdf (page 64), GRI report 2023.pdf (page 35), GRI report 2023.pdf (page 30), Client RFP deck.pdf (page 17), Bain DEI report.pdf (page 21), Bain DEI report.pdf (page 8), Full RFP FAQ Export.pdf (page 40), Client RFP deck.pdf (page 65), Client RFP deck.pdf (page 67), Client RFP deck.pdf (page 68), Client RFP deck.pdf (page 69), Client RFP deck.pdf (page 63), Client RFP deck.pdf (page 62), Professional Standards FAQ.pdf (page 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-05-30T09:40:17.935015</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>abhay singh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>The documents provided do not contain any information about an individual named Abhay Singh.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GRI report 2023.pdf (page 32), GRI report 2023.pdf (page 18), GRI report 2023.pdf (page 32), GRI report 2023.pdf (page 28), GRI report 2023.pdf (page 35), GRI report 2023.pdf (page 33), GRI report 2023.pdf (page 24), climate-transition-plan-2024.pdf (page 14), Client RFP deck.pdf (page 20), Bain Overview FAQ.pdf (page 2), Client RFP deck.pdf (page 52), Client RFP deck.pdf (page 63), Client RFP deck.pdf (page 41), Client RFP deck.pdf (page 67), Client RFP deck.pdf (page 15), Client RFP deck.pdf (page 65), Client RFP deck.pdf (page 66), human-rights-statement-05.2024.pdf (page 1), human-rights-statement-05.2024.pdf (page 1), sustainable-procurement-factsheet-v3-05.02.2024.pdf (page 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-05-30T09:41:34.906374</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>carbon integrity claim</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company's Carbon Integrity Claim refers to an assertion that the company complies with guidelines set by the Voluntary Carbon Markets Integrity Initiative (VCMI) for carbon emissions offsetting. Bain made a Carbon Integrity Platinum Claim for FY2023, the highest level possible under VCMI's guidelines. This means that Bain pledges to purchase and retire high-quality carbon removal credits in an amount greater than 100% of its annual residual Scopes 1, 2, and 3 emissions, adhering to the VCMI Claims Code of Practice. The claim confirms Bain's commitment to making climate actions beyond its net zero goal, ultimately contributing to mitigating climate change (2023_carbon-credit-disclosure.pdf, page 1; climate-transition-plan-2024.pdf, page 28).</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2023_carbon-credit-disclosure.pdf (page 1), climate-transition-plan-2024.pdf (page 28), 2023_carbon-credit-disclosure.pdf (page 3), 2023_carbon-credit-disclosure.pdf (page 1), GRI report 2023.pdf (page 70), Environmental-policy.pdf (page 2), GRI report 2023.pdf (page 21), GRI report 2023.pdf (page 58), climate-transition-plan-2024.pdf (page 7), GRI report 2023.pdf (page 22), GRI report 2023.pdf (page 70), GRI report 2023.pdf (page 21), climate-transition-plan-2024.pdf (page 15), climate-transition-plan-2024.pdf (page 8), bain-wef-and-tcfd-report-2023.pdf (page 6), bain-wef-and-tcfd-report-2023.pdf (page 19), bain-wef-and-tcfd-report-2023.pdf (page 29), Client RFP deck.pdf (page 29), Client RFP deck.pdf (page 43), Client RFP deck.pdf (page 35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-05-30T09:41:51.140735</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>carbon integrity claim</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>The Carbon Integrity Claim refers to Bain &amp; Company's commitment to high-integrity Beyond Value Chain Mitigation (BVCM), which involves buying and retiring carbon removal credits in quantities exceeding their annual residual Scope 1, 2, and 3 emissions. These high-quality carbon credits are subjected to rigorous due diligence in alignment with the Integrity Council for Voluntary Carbon Markets’ (ICVCM’s) Core Carbon Principles. Bain &amp; Company achieved a Carbon Integrity Platinum Claim for FY 2023 as defined by the Voluntary Carbon Markets Integrity Initiative (VCMI), meaning they purchased and retired carbon credits in an amount greater than 100% of their scope 1, 2, and 3 emissions. Bain asserts it has complied with the VCMI Claims Code of Practice's Foundational Criteria and all additional requirements (2023_carbon-credit-disclosure.pdf, page 1; Environmental-policy.pdf, page 2). Bain was also proud to be the first to make a Carbon Integrity Claim through the VCMI (climate-transition-plan-2024.pdf, page 28).</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2023_carbon-credit-disclosure.pdf (page 1), climate-transition-plan-2024.pdf (page 28), 2023_carbon-credit-disclosure.pdf (page 3), 2023_carbon-credit-disclosure.pdf (page 1), GRI report 2023.pdf (page 70), Environmental-policy.pdf (page 2), GRI report 2023.pdf (page 21), GRI report 2023.pdf (page 58), climate-transition-plan-2024.pdf (page 7), GRI report 2023.pdf (page 22), GRI report 2023.pdf (page 70), GRI report 2023.pdf (page 21), climate-transition-plan-2024.pdf (page 15), climate-transition-plan-2024.pdf (page 8), bain-wef-and-tcfd-report-2023.pdf (page 6), bain-wef-and-tcfd-report-2023.pdf (page 19), bain-wef-and-tcfd-report-2023.pdf (page 29), Client RFP deck.pdf (page 29), Client RFP deck.pdf (page 43), Client RFP deck.pdf (page 35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-05-30T10:25:21.235975</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>supplier form</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bain has a structured process for selecting and evaluating its suppliers. All new suppliers are evaluated through the Third-Party Risk Assessment (TPRA) process performed by Bain's Risk Committee, focusing on aspects such as corporate reputation, supplier capabilities, financial health, information security, and contractual elements. Any risks identified during this process may lead to the supplier being directed to perform remediation prior to engagement or prevented from providing services to Bain. This assessment covers all suppliers in Bain's global operations. 
+Bain has established a Supplier Code of Conduct that sets standards related to environmental commitments, ethical practices, and social responsibility. All suppliers are expected to comply with these guidelines. Any supplier violating this code may face termination of business relationship or might be asked to implement a corrective action plan. Details of Bain's expectations from suppliers, especially regarding sustainability, are also outlined in its Sustainable Procurement Policy. 
+Bain's procurement policy applies globally across all its activities and locations. The firm also engages with suppliers on environmental practices, has a grievance hotline for anonymous reporting of concerns, encourages supplier participation in its environmental and social impact efforts, and is committed to responsible sourcing. 
+For supplier diversity, Bain's U.S. Supplier Diversity Program aims to include small and diverse businesses in its procurement process and increase spending with such enterprises. The company reports on its diversity expenditure to clients on a quarterly basis, and it has Tier 2 reporting in place for its clients.
+Sources: GRI report 2023.pdf, page 4, Client RFP deck.pdf, pages 60, 64, 71, 73, 74, 75, 76, and 78, sustainable-procurement-factsheet-v3-05.02.2024.pdf, page 3.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GRI report 2023.pdf (page 4), Client RFP deck.pdf (page 74), Client RFP deck.pdf (page 76), Client RFP deck.pdf (page 16), GRI report 2023.pdf (page 13), Client RFP deck.pdf (page 72), Client RFP deck.pdf (page 73), Client RFP deck.pdf (page 75), Client RFP deck.pdf (page 3), Full RFP FAQ Export.pdf (page 1), Client RFP deck.pdf (page 71), Full RFP FAQ Export.pdf (page 33), Client RFP deck.pdf (page 62), Client RFP deck.pdf (page 1), Client RFP deck.pdf (page 21), Client RFP deck.pdf (page 64), sustainable-procurement-factsheet-v3-05.02.2024.pdf (page 3), human-rights-statement-05.2024.pdf (page 1), Diversity and Inclusion FAQ.pdf (page 9), Diversity and Inclusion FAQ.pdf (page 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-05-30T10:26:53.881185</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sbti </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>The Science Based Targets Initiative (SBTi) is a partnership that champions science-based target setting in the business sector to boost companies' competitive advantage in the transition to a low-carbon economy. The firm, Bain &amp; Company, is actively involved with SBTi.
+Bain has set near-term and long-term net-zero targets aligned with SBTi guidelines. Near-term targets (approved by SBTi) aim to reduce scope 1 and 2 emissions by 30% by 2026 and scope 3 emissions intensity from business travel by 35% per FTE over the same time period. Long-term targets are to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 and reduce scope 3 GHG emissions 97% per FTE over the same time period, both from a 2019 base year. It has been reported that the current emissions (scope 1 and 2) are below SBTi target emission level (Client RFP deck.pdf, page 32).
+In addition to their internal goals, Bain collaborates with SBTi to develop training materials that assist other corporations in setting science-based targets (Client RFP deck.pdf, page 47). They also aim to encourage 65% of their priority suppliers to commit to SBTi targets by 2030 (climate-transition-plan-2024.pdf, page 17).
+In their work with clients, Bain aims to embed ESG in 100% of projects and discusses its ESG ambitions with all of its clients, including engaging each client in discussions about their carbon goals and science-based targets, in alignment with Bain's own commitments (Client RFP deck.pdf, page 26).</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Environmental-policy.pdf (page 2), Environmental-policy.pdf (page 4), GRI report 2023.pdf (page 17), Client RFP deck.pdf (page 42), GRI report 2023.pdf (page 32), GRI report 2023.pdf (page 33), climate-transition-plan-2024.pdf (page 17), Client RFP deck.pdf (page 47), climate-transition-plan-2024.pdf (page 12), climate-transition-plan-2024.pdf (page 25), Client RFP deck.pdf (page 27), Client RFP deck.pdf (page 32), Client RFP deck.pdf (page 67), Client RFP deck.pdf (page 76), Client RFP deck.pdf (page 26), Client RFP deck.pdf (page 47), Client RFP deck.pdf (page 29), Client RFP deck.pdf (page 66), Client RFP deck.pdf (page 73), Client RFP deck.pdf (page 50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-05-30T10:27:08.190852</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sbti target?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company has set near-term and long-term Science-Based Targets Initiative (SBTi) approved goals for reducing emissions. The near-term targets aim to reduce scope 1 and 2 emissions by 30% and scope 3 business travel emissions by 35% per employee by 2026, based on a 2019 baseline. The long-term targets involve reducing scope 1 and 2 greenhouse gas emissions by 90% and scope 3 greenhouse gas emissions by 97% per full-time employee by 2050, also compared to a 2019 baseline. Bain &amp; Company has committed to annually source 100% renewable electricity through 2050. The company's targets align with the efforts to limit the temperature increase to 1.5°C under the Paris Agreement (Source: Environmental-policy.pdf, page 2; climate-transition-plan-2024.pdf, page 6; GRI report 2023.pdf, page 21).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Environmental-policy.pdf (page 2), Client RFP deck.pdf (page 32), Client RFP deck.pdf (page 42), Environmental-policy.pdf (page 4), climate-transition-plan-2024.pdf (page 6), climate-transition-plan-2024.pdf (page 17), climate-transition-plan-2024.pdf (page 12), GRI report 2023.pdf (page 21), bain-wef-and-tcfd-report-2023.pdf (page 30), GRI report 2023.pdf (page 34), GRI report 2023.pdf (page 61), Environmental-policy.pdf (page 2), climate-transition-plan-2024.pdf (page 29), Client RFP deck.pdf (page 47), Full RFP FAQ Export.pdf (page 47), Client RFP deck.pdf (page 29), Client RFP deck.pdf (page 32), Client RFP deck.pdf (page 23), Client RFP deck.pdf (page 27), Client RFP deck.pdf (page 37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-05-30T10:27:43.086898</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sbti target?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes, Bain &amp; Company has set targets validated by the Science Based Targets initiative (SBTi). The company is committed to achieving net-zero greenhouse gas emissions across the value chain by 2050. Their near-term targets include reducing scope 1 and 2 emissions by 30% by 2026 from a 2019 base year, and reducing scope 3 GHG emissions from business travel by 35% per Full-Time Employee (FTE) over the same time period. The long-term targets comprise a commitment to reduce absolute scope 1 and 2 GHG emissions by 90% by 2050 from a 2019 base year, and to reduce scope 3 GHG emissions by 97% per FTE over the same period (Source: Environmental-policy.pdf, page 2; Client RFP deck.pdf, page 32; bain-wef-and-tcfd-report-2023.pdf, page 30; climate-transition-plan-2024.pdf, page 6).</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Environmental-policy.pdf (page 2), Client RFP deck.pdf (page 32), Client RFP deck.pdf (page 42), Environmental-policy.pdf (page 4), climate-transition-plan-2024.pdf (page 6), climate-transition-plan-2024.pdf (page 17), climate-transition-plan-2024.pdf (page 12), GRI report 2023.pdf (page 21), bain-wef-and-tcfd-report-2023.pdf (page 30), GRI report 2023.pdf (page 34), GRI report 2023.pdf (page 61), Environmental-policy.pdf (page 2), climate-transition-plan-2024.pdf (page 29), Client RFP deck.pdf (page 47), Full RFP FAQ Export.pdf (page 47), Client RFP deck.pdf (page 29), Client RFP deck.pdf (page 32), Client RFP deck.pdf (page 23), Client RFP deck.pdf (page 27), Client RFP deck.pdf (page 37)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
